--- a/survey_templates/033_public_law_knowledge_quiz--survey_templates.xlsx
+++ b/survey_templates/033_public_law_knowledge_quiz--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,10 +525,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>survey_questions</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>What is the purpose of the Public Law?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Select all that apply</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -538,7 +542,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -548,10 +552,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>question_one</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>What is the primary function of public law?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Select one option</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>no</t>
@@ -571,7 +579,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>first_question_answer</t>
+          <t>What is the correct answer?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,20 +592,24 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>first_page_note</t>
+          <t>second_page</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>first_page_note</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>What are the types of public law?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Select all that apply</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -607,17 +619,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>first_question_type</t>
+          <t>second_question</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>question_type</t>
+          <t>What is the definition of municipal law?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +642,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>second_page</t>
+          <t>second_question_answer</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>second_page</t>
+          <t>Second Question Answer</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,20 +665,24 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>second_question</t>
+          <t>third_page</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>question_two</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>What is the hierarchy of public law?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Select all that apply</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -681,12 +697,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>second_question_answer</t>
+          <t>third_question</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>second_question_answer</t>
+          <t>Third Question</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,15 +720,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>second_page_note</t>
+          <t>third_page_note</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>second_page_note</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Additional comments</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Any additional comments?</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -727,15 +747,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>second_question_type</t>
+          <t>fourth_page</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>question_type</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>What is the relationship between public law and public policy?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Select one option</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -745,17 +769,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>third_page</t>
+          <t>fourth_question</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>third_page</t>
+          <t>What is the correct relationship?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,20 +792,24 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>third_question</t>
+          <t>fourth_page_note</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>question_three</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Fourth Page Note</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Any additional comments?</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
@@ -791,20 +819,24 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>third_question_answer</t>
+          <t>fifth_page</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>third_question_answer</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>What is the role of public law in modern society?</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Select all that apply</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>no</t>
@@ -814,17 +846,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>third_page_note</t>
+          <t>fifth_question</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>third_page_note</t>
+          <t>Fifth Question</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,20 +869,24 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>third_question_type</t>
+          <t>fifth_page_note</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>question_type</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Fifth Page Note</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Any additional comments?</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>no</t>
@@ -860,228 +896,21 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>fourth_page</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>fourth_page</t>
+          <t>Submit</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>fourth_question</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>question_four</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>fourth_question_answer</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>fourth_question_answer</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>fourth_page_note</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>fourth_page_note</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>fourth_question_type</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>question_type</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>fifth_page</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>fifth_page</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>fifth_question</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>question_five</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>fifth_question_answer</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>fifth_question_answer</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>fifth_page_note</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>fifth_page_note</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>submit</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>submit</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +927,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +960,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>to_protect_individual_rights</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>To protect individual rights</t>
         </is>
       </c>
     </row>
@@ -1148,80 +977,80 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>to_regulate_commerce</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>To regulate commerce</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>first_question_type_choices</t>
+          <t>first_page_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>to_establish_public_order</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>To establish public order</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>first_question_type_choices</t>
+          <t>first_question_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>to_regulate_and_enforce_laws</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>To regulate and enforce laws</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>first_question_type_choices</t>
+          <t>first_question_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>to_interpret_and_implement_laws</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>To interpret and implement laws</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>second_page_choices</t>
+          <t>first_question_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>to_advise_and_educate_citizens</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>To advise and educate citizens</t>
         </is>
       </c>
     </row>
@@ -1233,63 +1062,63 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>municipal_law</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Municipal law</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>second_question_type_choices</t>
+          <t>second_page_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>state_law</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>State law</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>second_question_type_choices</t>
+          <t>second_page_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>federal_law</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Federal law</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>second_question_type_choices</t>
+          <t>third_page_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>federal_laws</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>Federal laws</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1130,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>state_laws</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>State laws</t>
         </is>
       </c>
     </row>
@@ -1318,231 +1147,163 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>local_laws</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Local laws</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>third_question_type_choices</t>
+          <t>fourth_page_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>public_law_guides_public_policy</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Public law guides public policy</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>third_question_type_choices</t>
+          <t>fourth_page_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>public_policy_guides_public_law</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Public policy guides public law</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>third_question_type_choices</t>
+          <t>fourth_page_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>public_law_and_public_policy_are_independent</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>Public law and public policy are independent</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>fourth_page_choices</t>
+          <t>fifth_page_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>to_maintain_public_order</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>To maintain public order</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>fourth_page_choices</t>
+          <t>fifth_page_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>to_protect_individual_rights</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>To protect individual rights</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>fourth_question_type_choices</t>
+          <t>fifth_page_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>to_facilitate_commerce</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>To facilitate commerce</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>fourth_question_type_choices</t>
+          <t>submit_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Submit</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>fourth_question_type_choices</t>
+          <t>submit_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>cancel</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>Cancel</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>fifth_page_choices</t>
+          <t>submit_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>back</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>fifth_page_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>submit_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>submit</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Submit</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>submit_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>cancel</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Cancel</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>submit_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>back</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
         <is>
           <t>Back</t>
         </is>
